--- a/Base de Dados - Estoque.xlsx
+++ b/Base de Dados - Estoque.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Renato Milhomem\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Renato Milhomem\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AC5FE82-BF28-4A18-BFED-036DC01B15E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A02B6BE-8B88-4378-9E70-676B794884DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{259F4512-1A55-4DBA-B40A-E7CD17FF3C83}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="Análise-Dados-Estoque" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>CONSOLIDADO MENSAL E GIRO DE ESTOQUE</t>
   </si>
@@ -99,27 +99,50 @@
   </si>
   <si>
     <t>DEZ</t>
+  </si>
+  <si>
+    <t>Fill Rate</t>
+  </si>
+  <si>
+    <t>Cobertura</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4D4D4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5753F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -127,18 +150,71 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF5753F9"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -345,215 +421,348 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F5A85C0-1417-4DA6-8771-06B92BEF4E50}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="B2:J16"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="4.796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.09765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.8984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.8984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.3984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.8984375" customWidth="1"/>
+    <col min="5" max="5" width="6.8984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.8984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" t="s">
+    <row r="2" spans="2:10">
+      <c r="B2" s="7" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+    </row>
+    <row r="3" spans="2:10">
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+    </row>
+    <row r="4" spans="2:10">
+      <c r="B4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H4" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
+      <c r="I4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10">
+      <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4">
+      <c r="C5" s="2">
         <v>10000</v>
       </c>
-      <c r="C4">
+      <c r="D5" s="2">
         <v>8500</v>
       </c>
-      <c r="D4">
+      <c r="E5" s="2">
         <v>8095</v>
       </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+    </row>
+    <row r="6" spans="2:10">
+      <c r="B6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5">
-        <v>10405</v>
-      </c>
-      <c r="C5">
+      <c r="C6" s="2"/>
+      <c r="D6" s="2">
         <v>7600</v>
       </c>
-      <c r="D5">
+      <c r="E6" s="2">
         <v>7483</v>
       </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+    </row>
+    <row r="7" spans="2:10">
+      <c r="B7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6">
-        <v>10522</v>
-      </c>
-      <c r="C6">
+      <c r="C7" s="2"/>
+      <c r="D7" s="2">
         <v>9000</v>
       </c>
-      <c r="D6">
+      <c r="E7" s="2">
         <v>8734</v>
       </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" t="s">
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+    </row>
+    <row r="8" spans="2:10">
+      <c r="B8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B7">
-        <v>10788</v>
-      </c>
-      <c r="C7">
+      <c r="C8" s="2"/>
+      <c r="D8" s="2">
         <v>8600</v>
       </c>
-      <c r="D7">
+      <c r="E8" s="2">
         <v>8899</v>
       </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" t="s">
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+    </row>
+    <row r="9" spans="2:10">
+      <c r="B9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B8">
-        <v>10489</v>
-      </c>
-      <c r="C8">
+      <c r="C9" s="2"/>
+      <c r="D9" s="2">
         <v>9200</v>
       </c>
-      <c r="D8">
+      <c r="E9" s="2">
         <v>9141</v>
       </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" t="s">
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+    </row>
+    <row r="10" spans="2:10">
+      <c r="B10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B9">
-        <v>10548</v>
-      </c>
-      <c r="C9">
+      <c r="C10" s="2"/>
+      <c r="D10" s="2">
         <v>8500</v>
       </c>
-      <c r="D9">
+      <c r="E10" s="2">
         <v>8599</v>
       </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" t="s">
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+    </row>
+    <row r="11" spans="2:10">
+      <c r="B11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B10">
-        <v>10449</v>
-      </c>
-      <c r="C10">
+      <c r="C11" s="2"/>
+      <c r="D11" s="2">
         <v>9000</v>
       </c>
-      <c r="D10">
+      <c r="E11" s="2">
         <v>8988</v>
       </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" t="s">
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+    </row>
+    <row r="12" spans="2:10">
+      <c r="B12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B11">
-        <v>10461</v>
-      </c>
-      <c r="C11">
+      <c r="C12" s="2"/>
+      <c r="D12" s="2">
         <v>8700</v>
       </c>
-      <c r="D11">
+      <c r="E12" s="2">
         <v>8811</v>
       </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" t="s">
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+    </row>
+    <row r="13" spans="2:10">
+      <c r="B13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B12">
-        <v>10350</v>
-      </c>
-      <c r="C12">
+      <c r="C13" s="2"/>
+      <c r="D13" s="2">
         <v>9300</v>
       </c>
-      <c r="D12">
+      <c r="E13" s="2">
         <v>9158</v>
       </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" t="s">
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+    </row>
+    <row r="14" spans="2:10">
+      <c r="B14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B13">
-        <v>10492</v>
-      </c>
-      <c r="C13">
+      <c r="C14" s="2"/>
+      <c r="D14" s="2">
         <v>9200</v>
       </c>
-      <c r="D13">
+      <c r="E14" s="2">
         <v>9437</v>
       </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" t="s">
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+    </row>
+    <row r="15" spans="2:10">
+      <c r="B15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B14">
-        <v>10255</v>
-      </c>
-      <c r="C14">
+      <c r="C15" s="2"/>
+      <c r="D15" s="2">
         <v>10000</v>
       </c>
-      <c r="D14">
+      <c r="E15" s="2">
         <v>9629</v>
       </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" t="s">
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+    </row>
+    <row r="16" spans="2:10">
+      <c r="B16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B15">
-        <v>10626</v>
-      </c>
-      <c r="C15">
+      <c r="C16" s="2"/>
+      <c r="D16" s="2">
         <v>10500</v>
       </c>
-      <c r="D15">
+      <c r="E16" s="2">
         <v>10839</v>
       </c>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:J3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{05C60535-1F16-4fd2-B633-F4F36F0B64E0}">
+      <x14:sparklineGroups xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+        <x14:sparklineGroup displayEmptyCellsAs="span" xr2:uid="{AF608C62-F270-433C-8811-23834C782A97}">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'Análise-Dados-Estoque'!H5:H5</xm:f>
+              <xm:sqref>I5</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Análise-Dados-Estoque'!H6:H6</xm:f>
+              <xm:sqref>I6</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Análise-Dados-Estoque'!H7:H7</xm:f>
+              <xm:sqref>I7</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Análise-Dados-Estoque'!H8:H8</xm:f>
+              <xm:sqref>I8</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Análise-Dados-Estoque'!H9:H9</xm:f>
+              <xm:sqref>I9</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Análise-Dados-Estoque'!H10:H10</xm:f>
+              <xm:sqref>I10</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Análise-Dados-Estoque'!H11:H11</xm:f>
+              <xm:sqref>I11</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Análise-Dados-Estoque'!H12:H12</xm:f>
+              <xm:sqref>I12</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Análise-Dados-Estoque'!H13:H13</xm:f>
+              <xm:sqref>I13</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Análise-Dados-Estoque'!H14:H14</xm:f>
+              <xm:sqref>I14</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Análise-Dados-Estoque'!H15:H15</xm:f>
+              <xm:sqref>I15</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Análise-Dados-Estoque'!H16:H16</xm:f>
+              <xm:sqref>I16</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+      </x14:sparklineGroups>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
--- a/Base de Dados - Estoque.xlsx
+++ b/Base de Dados - Estoque.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Renato Milhomem\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Renato Milhomem\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A02B6BE-8B88-4378-9E70-676B794884DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BF62EC5-BAF2-4ECC-903D-1D8B023CF0AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{259F4512-1A55-4DBA-B40A-E7CD17FF3C83}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>CONSOLIDADO MENSAL E GIRO DE ESTOQUE</t>
   </si>
@@ -105,6 +105,27 @@
   </si>
   <si>
     <t>Cobertura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custo por pedido </t>
+  </si>
+  <si>
+    <t>Custo de manter estoque</t>
+  </si>
+  <si>
+    <t>Demanda Anual</t>
+  </si>
+  <si>
+    <t>EOQ (unidades por pedido)</t>
+  </si>
+  <si>
+    <t>Número de pedidos (demanda/EOQ)</t>
+  </si>
+  <si>
+    <t>Intervalo entre pedidos (365/Nº pedidos)</t>
+  </si>
+  <si>
+    <t>Giro de Estoque Anual</t>
   </si>
 </sst>
 </file>
@@ -122,7 +143,7 @@
       <name val="Carlito"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -138,6 +159,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF5753F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -193,7 +226,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -204,6 +237,14 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -421,7 +462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F5A85C0-1417-4DA6-8771-06B92BEF4E50}">
-  <dimension ref="B2:J16"/>
+  <dimension ref="B2:J23"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="4.796875" bestFit="1" customWidth="1"/>
@@ -429,7 +470,7 @@
     <col min="4" max="4" width="15.8984375" customWidth="1"/>
     <col min="5" max="5" width="6.8984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.8984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.5" customWidth="1"/>
     <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.09765625" bestFit="1" customWidth="1"/>
   </cols>
@@ -462,13 +503,13 @@
       <c r="B4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="4" t="s">
@@ -692,6 +733,48 @@
       <c r="H16" s="3"/>
       <c r="I16" s="5"/>
       <c r="J16" s="5"/>
+    </row>
+    <row r="19" spans="4:8">
+      <c r="D19" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="3">
+        <v>40</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H19" s="10"/>
+    </row>
+    <row r="20" spans="4:8" ht="27.6">
+      <c r="D20" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="3">
+        <v>4</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="H20" s="10"/>
+    </row>
+    <row r="21" spans="4:8">
+      <c r="G21" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H21" s="10"/>
+    </row>
+    <row r="22" spans="4:8">
+      <c r="G22" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="H22" s="10"/>
+    </row>
+    <row r="23" spans="4:8">
+      <c r="G23" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="H23" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">
